--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251130_201204.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251130_201204.xlsx
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251130_201204.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251130_201204.xlsx
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
